--- a/public/template/foreign-route-approval/approval-template.xlsx
+++ b/public/template/foreign-route-approval/approval-template.xlsx
@@ -1545,7 +1545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G341"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="3"/>
@@ -5725,6 +5725,30 @@
       <c r="B341" s="6" t="inlineStr">
         <is>
           <t>BFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>墨西哥城空运机场</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>NLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>墨西哥城国际</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>MEX</t>
         </is>
       </c>
     </row>
